--- a/Revision/01_需蔡老師補做資料表/included_vs_excluded_insufficient_followup.xlsx
+++ b/Revision/01_需蔡老師補做資料表/included_vs_excluded_insufficient_followup.xlsx
@@ -728,7 +728,11 @@
           <t>1815 (6.6%)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>NA</t>
@@ -746,7 +750,11 @@
           <t>Approved beds</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>80.0 (54.5)</t>
@@ -769,7 +777,11 @@
           <t>Small facility (&lt;50 beds)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>8996 (47.1%)</t>
@@ -792,7 +804,11 @@
           <t>Large facility (&gt;150 beds)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>2115 (11.1%)</t>
